--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_148_R15.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_148_R15.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.998900000000001</v>
+        <v>9.3596</v>
       </c>
       <c r="E2" t="n">
-        <v>7.9694</v>
+        <v>8.162100000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0295</v>
+        <v>1.1975</v>
       </c>
       <c r="G2" t="n">
         <v>7.879</v>
@@ -610,13 +610,13 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5759</v>
+        <v>-0.2153</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1766</v>
+        <v>0.016</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3993</v>
+        <v>-0.2313</v>
       </c>
       <c r="V2" t="n">
         <v>0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6083</v>
+        <v>5.4917</v>
       </c>
       <c r="E3" t="n">
-        <v>6.2495</v>
+        <v>6.6033</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6411</v>
+        <v>-1.1116</v>
       </c>
       <c r="G3" t="n">
         <v>4.4359</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3348</v>
+        <v>0.2181</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5895</v>
+        <v>-0.2357</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9243</v>
+        <v>0.4538</v>
       </c>
       <c r="V3" t="n">
         <v>0.1418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. SHENGELIA</t>
+          <t>J. VESELY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6396</v>
+        <v>3.0574</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5052</v>
+        <v>2.4731</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1345</v>
+        <v>0.5843</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5961</v>
+        <v>0.8165</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6988</v>
+        <v>-0.6424</v>
       </c>
       <c r="I4" t="n">
-        <v>1.295</v>
+        <v>1.4589</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1399</v>
+        <v>1.3495</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4173</v>
+        <v>0.1484</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7227</v>
+        <v>1.2011</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5438</v>
+        <v>-0.533</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1161</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5723</v>
+        <v>0.2578</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.0876</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5515</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9017</v>
+        <v>0.1533</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7027</v>
+        <v>0.2833</v>
       </c>
       <c r="U4" t="n">
-        <v>0.199</v>
+        <v>-0.13</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
         <v>-1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. VESELY</t>
+          <t>T. SATORANSKY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6123</v>
+        <v>2.283</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1625</v>
+        <v>1.595</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4498</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8165</v>
+        <v>0.3804</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6424</v>
+        <v>-0.63</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4589</v>
+        <v>1.0104</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3495</v>
+        <v>1.3138</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1484</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2011</v>
+        <v>0.8062</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.533</v>
+        <v>-0.9334</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-1.1377</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2578</v>
+        <v>0.2042</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
         <v>2.3195</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2917</v>
+        <v>1.3691</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0272</v>
+        <v>0.995</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2645</v>
+        <v>0.3741</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X5" t="n">
         <v>-1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>T. SHENGELIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7801</v>
+        <v>2.0402</v>
       </c>
       <c r="E6" t="n">
-        <v>2.4581</v>
+        <v>0.8721</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.678</v>
+        <v>1.1681</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2723</v>
+        <v>0.5961</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6264999999999999</v>
+        <v>-0.6988</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6458</v>
+        <v>1.295</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6823</v>
+        <v>1.1399</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0672</v>
+        <v>0.4173</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.7227</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.59</v>
+        <v>-0.5438</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6938</v>
+        <v>-1.1161</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1038</v>
+        <v>0.5723</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R6" t="n">
-        <v>0.232</v>
+        <v>2.5515</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5163</v>
+        <v>1.3023</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3002</v>
+        <v>1.0697</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2161</v>
+        <v>0.2326</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>1.214</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. SATORANSKY</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7358</v>
+        <v>1.265</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8126</v>
+        <v>1.943</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9232</v>
+        <v>-0.678</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3804</v>
+        <v>-1.2723</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.63</v>
+        <v>-0.6264999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0104</v>
+        <v>-0.6458</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3138</v>
+        <v>-0.6823</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.0672</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8062</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9334</v>
+        <v>-0.59</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1377</v>
+        <v>-0.6938</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2042</v>
+        <v>0.1038</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8219</v>
+        <v>2.0012</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2126</v>
+        <v>1.7851</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6093</v>
+        <v>0.2161</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3943</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>W. HERNANGOMEZ</t>
+          <t>J. MARCOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.052</v>
+        <v>-1.4015</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5501</v>
+        <v>-0.5286</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6021</v>
+        <v>-0.8729</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.6521</v>
+        <v>-1.5988</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.0097</v>
+        <v>-0.3072</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6424</v>
+        <v>-1.2916</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.1579</v>
+        <v>-0.6623</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3051</v>
+        <v>0.0504</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1472</v>
+        <v>-0.7127</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4942</v>
+        <v>-0.9365</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7045</v>
+        <v>-0.3577</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7896</v>
+        <v>-0.5788</v>
       </c>
       <c r="P9" t="n">
         <v>0.232</v>
@@ -1156,28 +1156,28 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8346</v>
+        <v>0.1072</v>
       </c>
       <c r="T9" t="n">
-        <v>3.7982</v>
+        <v>0.3657</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0365</v>
+        <v>-0.2585</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4665</v>
+        <v>-0.1418</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.6083</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MARCOS</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0995</v>
+        <v>-2.7128</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.193</v>
+        <v>-1.3149</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9065</v>
+        <v>-1.3979</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5988</v>
+        <v>-2.7881</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3072</v>
+        <v>-1.9148</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2916</v>
+        <v>-0.8733</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6623</v>
+        <v>-1.462</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0504</v>
+        <v>-1.5356</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7127</v>
+        <v>0.0736</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9365</v>
+        <v>-1.3261</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3577</v>
+        <v>-0.3792</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5788</v>
+        <v>-0.9469</v>
       </c>
       <c r="P10" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-1.3917</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.232</v>
       </c>
-      <c r="Q10" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.4639</v>
-      </c>
       <c r="S10" t="n">
-        <v>-0.5909</v>
+        <v>0.6989</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2987</v>
+        <v>1.0027</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2921</v>
+        <v>-0.3038</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5345</v>
+        <v>-2.7396</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0357</v>
+        <v>-0.5914</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4987</v>
+        <v>-2.1481</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7881</v>
+        <v>-0.8862</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.9148</v>
+        <v>-1.2509</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8733</v>
+        <v>0.3647</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.462</v>
+        <v>-0.5249</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.5356</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0736</v>
+        <v>0.1571</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3261</v>
+        <v>-0.3613</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3792</v>
+        <v>-0.5688</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9469</v>
+        <v>0.2075</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.3917</v>
       </c>
       <c r="R11" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8773</v>
+        <v>0.9869</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2819</v>
+        <v>1.3251</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4046</v>
+        <v>-0.3383</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5361</v>
+        <v>-2.1444</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>W. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6912</v>
+        <v>-2.8981</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2742</v>
+        <v>-0.2625</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.417</v>
+        <v>-2.6357</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8862</v>
+        <v>-3.6521</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2509</v>
+        <v>-3.0097</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3647</v>
+        <v>-0.6424</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.5249</v>
+        <v>-2.1579</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-2.3051</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1571</v>
+        <v>0.1472</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3613</v>
+        <v>-1.4942</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5688</v>
+        <v>-0.7045</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2075</v>
+        <v>-0.7896</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9647</v>
+        <v>1.9885</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3576</v>
+        <v>1.9856</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6071</v>
+        <v>0.0029</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1444</v>
+        <v>-1.4665</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1444</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.856</v>
+        <v>13.6031</v>
       </c>
       <c r="E13" t="n">
-        <v>18.2045</v>
+        <v>18.9512</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.348199999999999</v>
+        <v>-5.3481</v>
       </c>
       <c r="G13" t="n">
         <v>3.910399999999999</v>
@@ -1444,7 +1444,7 @@
         <v>13.2599</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4407</v>
+        <v>-0.4407000000000001</v>
       </c>
       <c r="L13" t="n">
         <v>13.7008</v>
@@ -1453,13 +1453,13 @@
         <v>-9.349499999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.476699999999999</v>
+        <v>-7.4767</v>
       </c>
       <c r="O13" t="n">
         <v>-1.8729</v>
       </c>
       <c r="P13" t="n">
-        <v>3.4794</v>
+        <v>3.479400000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.438</v>
@@ -1468,13 +1468,13 @@
         <v>13.9173</v>
       </c>
       <c r="S13" t="n">
-        <v>7.863400000000001</v>
+        <v>8.610200000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>7.846</v>
+        <v>8.592499999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01759999999999984</v>
+        <v>0.01759999999999994</v>
       </c>
       <c r="V13" t="n">
         <v>-2.3969</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3343</v>
+        <v>3.0763</v>
       </c>
       <c r="E14" t="n">
-        <v>4.9749</v>
+        <v>4.5031</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6406</v>
+        <v>-1.4268</v>
       </c>
       <c r="G14" t="n">
         <v>-2.2118</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2245</v>
+        <v>-0.4826</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5351</v>
+        <v>0.0633</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7595</v>
+        <v>-0.5458</v>
       </c>
       <c r="V14" t="n">
         <v>4.147</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>A. PETERS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0446</v>
+        <v>1.8934</v>
       </c>
       <c r="E15" t="n">
-        <v>2.7928</v>
+        <v>2.6207</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7482</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7219</v>
+        <v>1.088</v>
       </c>
       <c r="H15" t="n">
-        <v>2.9063</v>
+        <v>1.7036</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1844</v>
+        <v>-0.6156</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8043</v>
+        <v>0.602</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4066</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.0871</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.0824</v>
+        <v>0.4861</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4997</v>
+        <v>1.0146</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5821</v>
+        <v>-0.5286</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8588</v>
+        <v>-1.0528</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6122</v>
+        <v>-0.1256</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7534</v>
+        <v>-0.9271</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5361</v>
+        <v>0.9304</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5361</v>
+        <v>2.1444</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PETERS</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1851</v>
+        <v>0.8328</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1489</v>
+        <v>1.6133</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9638</v>
+        <v>-0.7805</v>
       </c>
       <c r="G16" t="n">
-        <v>1.088</v>
+        <v>1.7219</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7036</v>
+        <v>2.9063</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6156</v>
+        <v>-1.1844</v>
       </c>
       <c r="J16" t="n">
-        <v>0.602</v>
+        <v>1.8043</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6889999999999999</v>
+        <v>2.4066</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0871</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4861</v>
+        <v>-0.0824</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0146</v>
+        <v>0.4997</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5286</v>
+        <v>-0.5821</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7611</v>
+        <v>-0.353</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5975</v>
+        <v>0.4327</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1637</v>
+        <v>-0.7857</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9304</v>
+        <v>-0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>2.1444</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.6681</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9616</v>
+        <v>1.136</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0394</v>
+        <v>-1.8041</v>
       </c>
       <c r="G17" t="n">
         <v>-1.3463</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6603</v>
+        <v>0.0698</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0578</v>
+        <v>0.2322</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3976</v>
+        <v>-0.1623</v>
       </c>
       <c r="V17" t="n">
         <v>1.0722</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7799</v>
+        <v>-1.4768</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9851</v>
+        <v>-0.9177999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-0.8994</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5764</v>
+        <v>-0.2732</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1494</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.427</v>
+        <v>-0.3598</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5361</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.7022</v>
+        <v>-1.9324</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0852</v>
+        <v>0.5046</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.617</v>
+        <v>-2.4369</v>
       </c>
       <c r="G19" t="n">
         <v>-1.7486</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8092</v>
+        <v>-0.0393</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8136</v>
+        <v>-0.2238</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0044</v>
+        <v>0.1845</v>
       </c>
       <c r="V19" t="n">
         <v>-1.0722</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>E. FOURNIER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8812</v>
+        <v>-2.3204</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2323</v>
+        <v>-0.3258</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.649</v>
+        <v>-1.9946</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0121</v>
+        <v>0.6701</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1861</v>
+        <v>1.2857</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.174</v>
+        <v>-0.6156</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0872</v>
+        <v>2.2998</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0504</v>
+        <v>0.9649</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0368</v>
+        <v>1.3349</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0751</v>
+        <v>-1.6297</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1357</v>
+        <v>0.3209</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2108</v>
+        <v>-1.9505</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0876</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2697</v>
+        <v>-1.3642</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.4479</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2697</v>
+        <v>-0.9164</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>-0.9304</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3683</v>
+        <v>-2.6961</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5478</v>
+        <v>-2.1143</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.8205</v>
+        <v>-0.5817</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8290999999999999</v>
+        <v>0.0121</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.461</v>
+        <v>0.1861</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.368</v>
+        <v>-0.174</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3554</v>
+        <v>0.0872</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1205</v>
+        <v>0.0504</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4759</v>
+        <v>0.0368</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1844</v>
+        <v>-0.0751</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3405</v>
+        <v>0.1357</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.8439</v>
+        <v>-0.2108</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.4793</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.871</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9208</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1766</v>
+        <v>0.118</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7442</v>
+        <v>-0.2025</v>
       </c>
       <c r="V21" t="n">
-        <v>1.8608</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2836</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. FOURNIER</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6508</v>
+        <v>-2.9586</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9156</v>
+        <v>-0.4298</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.7352</v>
+        <v>-2.5288</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6701</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2857</v>
+        <v>-0.461</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6156</v>
+        <v>-0.368</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2998</v>
+        <v>2.3554</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9649</v>
+        <v>-0.1205</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3349</v>
+        <v>2.4759</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.6297</v>
+        <v>-3.1844</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3209</v>
+        <v>-0.3405</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9505</v>
+        <v>-2.8439</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.3195</v>
+        <v>-4.871</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6237</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.6947</v>
+        <v>-0.5111</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0376</v>
+        <v>-0.0587</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.657</v>
+        <v>-0.4525</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.9304</v>
+        <v>1.8608</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9601</v>
+        <v>-4.2473</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9543</v>
+        <v>-1.6004</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0058</v>
+        <v>-2.6469</v>
       </c>
       <c r="G23" t="n">
         <v>-0.3674</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.1262</v>
+        <v>-1.4134</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4481</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.6781</v>
+        <v>-1.3192</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0026</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-12.8562</v>
+        <v>-10.4972</v>
       </c>
       <c r="E24" t="n">
-        <v>5.348100000000001</v>
+        <v>5.348399999999998</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.2046</v>
+        <v>-15.8454</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9105</v>
@@ -2302,7 +2302,7 @@
         <v>9.349600000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>7.476800000000001</v>
+        <v>7.4768</v>
       </c>
       <c r="L24" t="n">
         <v>1.8729</v>
@@ -2311,13 +2311,13 @@
         <v>-13.26</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4406999999999999</v>
+        <v>0.4406999999999998</v>
       </c>
       <c r="O24" t="n">
         <v>-13.7007</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.4793</v>
+        <v>-3.479299999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-13.9172</v>
@@ -2326,13 +2326,13 @@
         <v>10.438</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.8635</v>
+        <v>-5.5044</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.01769999999999988</v>
+        <v>-0.01750000000000015</v>
       </c>
       <c r="U24" t="n">
-        <v>-7.8458</v>
+        <v>-5.486800000000001</v>
       </c>
       <c r="V24" t="n">
         <v>2.3969</v>
@@ -2341,7 +2341,7 @@
         <v>9.933399999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.536500000000001</v>
+        <v>-7.5365</v>
       </c>
     </row>
   </sheetData>
